--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T13:05:17+00:00</t>
+    <t>2025-10-30T16:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T16:35:25+00:00</t>
+    <t>2025-10-30T16:59:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T16:59:01+00:00</t>
+    <t>2025-10-30T17:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T17:21:27+00:00</t>
+    <t>2025-10-30T20:58:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T20:58:23+00:00</t>
+    <t>2025-10-30T21:07:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T21:07:17+00:00</t>
+    <t>2025-10-31T10:04:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T10:04:57+00:00</t>
+    <t>2025-10-31T10:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T10:52:01+00:00</t>
+    <t>2025-10-31T10:55:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T10:55:25+00:00</t>
+    <t>2025-10-31T13:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T13:28:44+00:00</t>
+    <t>2025-10-31T13:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T13:29:03+00:00</t>
+    <t>2025-10-31T16:13:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T16:13:56+00:00</t>
+    <t>2025-10-31T16:25:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T16:25:02+00:00</t>
+    <t>2025-10-31T16:31:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T16:31:50+00:00</t>
+    <t>2025-10-31T16:48:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T16:48:30+00:00</t>
+    <t>2025-11-01T12:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
+++ b/nr-create-ig/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-01T12:02:40+00:00</t>
+    <t>2025-11-07T10:30:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
